--- a/public/templates/supplier.xlsx
+++ b/public/templates/supplier.xlsx
@@ -49,7 +49,7 @@
       <color rgb="FFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none">
         <bgColor/>
@@ -63,6 +63,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF2563EB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCCCCC"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -101,13 +107,14 @@
   <cellStyleXfs>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="1" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -490,37 +497,37 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="str">
+      <c r="A2" s="4" t="str">
         <v>SUP-001</v>
       </c>
-      <c r="B2" s="2" t="str">
+      <c r="B2" s="4" t="str">
         <v>PT Sumber Rejeki</v>
       </c>
-      <c r="C2" s="2" t="str">
+      <c r="C2" s="4" t="str">
         <v>021-777-1000</v>
       </c>
-      <c r="D2" s="2" t="str">
+      <c r="D2" s="4" t="str">
         <v>sales@sumberrejeki.co.id</v>
       </c>
-      <c r="E2" s="2" t="str">
+      <c r="E2" s="4" t="str">
         <v>Budi Santoso</v>
       </c>
-      <c r="F2" s="2" t="str">
+      <c r="F2" s="4" t="str">
         <v>Jl. Industri No. 10</v>
       </c>
-      <c r="G2" s="2" t="str">
+      <c r="G2" s="4" t="str">
         <v>Jakarta</v>
       </c>
-      <c r="H2" s="2" t="str">
+      <c r="H2" s="4" t="str">
         <v>DKI Jakarta</v>
       </c>
-      <c r="I2" s="2" t="str">
+      <c r="I2" s="4" t="str">
         <v>13920</v>
       </c>
-      <c r="J2" s="2" t="str">
+      <c r="J2" s="4" t="str">
         <v>Indonesia</v>
       </c>
-      <c r="K2" s="2" t="b">
+      <c r="K2" s="4" t="b">
         <v>1</v>
       </c>
     </row>
